--- a/data/trans_camb/IQ2601_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IQ2601_R2-Provincia-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-14,81</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5,47</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-18,1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,17</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>15,27</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-14,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,09</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>13,82</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>10,37</t>
+          <t>8,89</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,87; -2,07</t>
+          <t>-29,96; 0,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-13,66; 16,11</t>
+          <t>-15,16; 14,03</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 34,79</t>
+          <t>-18,13; 25,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,59; 0,57</t>
+          <t>-33,22; -1,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 13,15</t>
+          <t>-15,36; 15,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-16,53; 27,29</t>
+          <t>-9,68; 34,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-27,46; -6,27</t>
+          <t>-27,22; -5,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 10,54</t>
+          <t>-11,34; 10,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,94; 25,44</t>
+          <t>-9,39; 23,79</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-24,75%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-1,83%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>9,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-29,93%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,93%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>25,25%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-24,75%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-1,83%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>14,78%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,85; -4,71</t>
+          <t>-44,29; 1,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,7; 31,5</t>
+          <t>-22,84; 28,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 68,82</t>
+          <t>-28,31; 45,54</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,95; 1,11</t>
+          <t>-49,78; -1,85</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-22,59; 25,98</t>
+          <t>-22,94; 28,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 52,19</t>
+          <t>-14,36; 63,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-41,97; -11,15</t>
+          <t>-42,22; -9,75</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,11; 18,78</t>
+          <t>-16,9; 18,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 47,12</t>
+          <t>-14,55; 42,44</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-50,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-32,44</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-30,92</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-38,35</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-26,84</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-16,6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-50,27</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-32,44</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-30,42</t>
+          <t>-20,62</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-24,4</t>
+          <t>-26,35</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-47,82; -28,43</t>
+          <t>-58,59; -41,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-35,84; -17,95</t>
+          <t>-40,62; -24,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-35,34; -1,2</t>
+          <t>-49,48; -12,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-58,5; -41,22</t>
+          <t>-47,81; -28,52</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-40,54; -23,92</t>
+          <t>-35,5; -17,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-49,0; -12,16</t>
+          <t>-39,22; -4,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-50,94; -38,22</t>
+          <t>-50,55; -38,25</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-35,8; -23,69</t>
+          <t>-35,58; -23,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,42; -11,4</t>
+          <t>-40,49; -14,29</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-53,19%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-34,32%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-32,72%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-43,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-30,17%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,66%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-53,19%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-34,32%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-32,18%</t>
+          <t>-23,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-26,55%</t>
+          <t>-28,67%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,6; -33,02</t>
+          <t>-61,41; -44,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,83; -20,91</t>
+          <t>-42,93; -26,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-39,7; -1,47</t>
+          <t>-52,14; -13,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-61,39; -44,41</t>
+          <t>-52,38; -33,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,43; -25,73</t>
+          <t>-39,02; -20,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,05; -13,17</t>
+          <t>-43,48; -4,78</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-55,61; -42,64</t>
+          <t>-54,48; -42,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-38,46; -26,23</t>
+          <t>-38,03; -25,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-40,72; -12,47</t>
+          <t>-44,36; -15,65</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,71</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>33,6</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24,87</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-7,7</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>16,77</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12,31</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,71</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>33,6</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>26,64</t>
+          <t>11,62</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>19,58</t>
+          <t>18,4</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 7,23</t>
+          <t>-13,14; 12,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,96; 30,61</t>
+          <t>20,85; 46,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 31,86</t>
+          <t>2,32; 44,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 11,36</t>
+          <t>-21,61; 6,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>20,87; 45,61</t>
+          <t>3,06; 30,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,18; 44,82</t>
+          <t>-9,47; 30,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-14,42; 5,84</t>
+          <t>-14,37; 4,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>15,27; 35,17</t>
+          <t>14,82; 34,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 33,2</t>
+          <t>2,53; 31,7</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-4,76%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>93,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69,15%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-15,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>34,02%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24,97%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-4,76%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>93,42%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>43,3%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-38,84; 16,94</t>
+          <t>-32,05; 40,38</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 75,2</t>
+          <t>49,11; 167,26</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,18; 74,87</t>
+          <t>6,49; 143,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,97; 37,43</t>
+          <t>-38,76; 16,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>48,22; 157,68</t>
+          <t>5,35; 73,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,13; 145,24</t>
+          <t>-16,7; 72,25</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-30,25; 14,64</t>
+          <t>-30,19; 12,29</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,34; 92,75</t>
+          <t>30,2; 91,1</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 86,64</t>
+          <t>5,67; 82,19</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3,6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9,29</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41,63</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-7,28</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-7,33</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,6</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,29</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,63</t>
+          <t>-6,75</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>14,58</t>
+          <t>14,37</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-13,92; 10,84</t>
+          <t>-9,13; 16,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-20,49; 5,73</t>
+          <t>-4,24; 21,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-36,71; 15,7</t>
+          <t>32,91; 50,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,41; 16,24</t>
+          <t>-13,0; 11,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 21,64</t>
+          <t>-18,88; 5,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,5; 49,32</t>
+          <t>-34,29; 15,21</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 9,6</t>
+          <t>-7,45; 10,2</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 10,03</t>
+          <t>-7,32; 10,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 28,18</t>
+          <t>-8,56; 29,06</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>15,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>71,32%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-1,89%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-10,36%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-10,44%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>15,91%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>-9,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,42%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 17,13</t>
+          <t>-14,33; 32,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-27,41; 8,87</t>
+          <t>-6,48; 40,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 22,76</t>
+          <t>49,06; 101,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,5; 31,97</t>
+          <t>-17,18; 17,21</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 41,57</t>
+          <t>-25,67; 7,73</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>48,14; 97,3</t>
+          <t>-47,31; 21,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 16,14</t>
+          <t>-10,73; 17,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-10,95; 16,78</t>
+          <t>-10,8; 17,5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-9,89; 47,41</t>
+          <t>-12,41; 47,18</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,05</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>16,34</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>40,68</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-7,59</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>16,33</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,05</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>16,34</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,68</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>22,14</t>
+          <t>22,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 8,78</t>
+          <t>-15,6; 18,46</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,47; 29,21</t>
+          <t>0,68; 32,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-19,85; 25,18</t>
+          <t>28,13; 53,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-16,0; 19,34</t>
+          <t>-23,75; 11,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,16; 31,08</t>
+          <t>1,67; 28,38</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29,65; 52,99</t>
+          <t>-21,5; 21,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 10,48</t>
+          <t>-14,68; 10,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>3,98; 27,0</t>
+          <t>4,81; 26,36</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7,75; 33,84</t>
+          <t>8,49; 33,0</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27,55%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>68,58%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-10,56%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>22,73%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3,66%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>27,55%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>33,9%</t>
+          <t>34,11%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-31,03; 14,65</t>
+          <t>-23,79; 36,49</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4,06; 47,51</t>
+          <t>1,0; 68,15</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-25,92; 39,22</t>
+          <t>39,15; 114,61</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-23,43; 39,14</t>
+          <t>-30,78; 20,07</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>0,24; 62,94</t>
+          <t>2,24; 45,56</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>42,15; 112,71</t>
+          <t>-27,45; 31,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 17,79</t>
+          <t>-21,06; 17,35</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>5,84; 47,07</t>
+          <t>6,68; 44,91</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>12,14; 58,08</t>
+          <t>12,08; 55,61</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-14,08</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>4,2</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>9,98</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-1,38</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>6,46</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>16,59</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-14,08</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>4,2</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,2</t>
+          <t>15,5</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>13,98</t>
+          <t>12,78</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 14,86</t>
+          <t>-28,94; 1,4</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,5; 20,73</t>
+          <t>-11,15; 18,62</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-11,13; 43,57</t>
+          <t>-12,98; 31,23</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 1,47</t>
+          <t>-16,79; 14,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-10,48; 18,87</t>
+          <t>-10,35; 21,11</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 32,51</t>
+          <t>-12,94; 41,59</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-19,53; 2,85</t>
+          <t>-17,39; 3,01</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 15,7</t>
+          <t>-5,07; 15,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 29,16</t>
+          <t>-3,67; 28,91</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-29,43%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>8,79%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>20,87%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-3,33%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>15,57%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>40,01%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-29,43%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>8,79%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>28,56%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-34,17; 45,92</t>
+          <t>-53,02; 3,63</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-17,49; 61,86</t>
+          <t>-20,56; 45,98</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 120,9</t>
+          <t>-25,66; 75,3</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-52,66; 3,67</t>
+          <t>-35,03; 43,39</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-19,89; 46,46</t>
+          <t>-20,28; 64,15</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-17,18; 78,89</t>
+          <t>-27,24; 115,93</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-38,69; 6,78</t>
+          <t>-36,09; 7,17</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,16; 39,52</t>
+          <t>-10,02; 40,91</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 70,14</t>
+          <t>-7,87; 72,22</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-15,63</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>3,66</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>8,65</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-13,44</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>2,82</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>8,98</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-15,63</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>3,66</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47</t>
+          <t>4,91</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>8,72</t>
+          <t>7,21</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-22,51; -2,96</t>
+          <t>-25,13; -5,38</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-6,04; 12,91</t>
+          <t>-6,47; 12,72</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 25,78</t>
+          <t>-5,89; 22,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-25,4; -5,8</t>
+          <t>-23,32; -2,63</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 12,33</t>
+          <t>-6,84; 12,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-8,07; 22,33</t>
+          <t>-14,02; 21,52</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -6,45</t>
+          <t>-21,44; -7,48</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 10,09</t>
+          <t>-3,65; 9,84</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 20,33</t>
+          <t>-4,76; 17,8</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-25,68%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>6,02%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>14,22%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-22,27%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>4,68%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>14,87%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-25,68%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>11,89%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-35,99; -5,9</t>
+          <t>-38,74; -9,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 23,92</t>
+          <t>-9,94; 22,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-11,76; 46,18</t>
+          <t>-9,23; 39,54</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-38,62; -9,95</t>
+          <t>-36,1; -5,14</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 22,02</t>
+          <t>-10,47; 22,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-12,39; 38,56</t>
+          <t>-22,87; 36,97</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,85; -11,44</t>
+          <t>-33,52; -12,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 17,91</t>
+          <t>-5,67; 17,3</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 34,87</t>
+          <t>-7,39; 30,37</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-17,54</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-10,55</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>8,54</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-19,0</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-12,95</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>-2,1</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-17,54</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-10,55</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,53</t>
+          <t>-1,79</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>4,09</t>
+          <t>4,2</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-27,74; -11,9</t>
+          <t>-25,31; -8,87</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-20,36; -4,74</t>
+          <t>-18,04; -1,77</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 11,51</t>
+          <t>-6,52; 18,19</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-25,58; -9,77</t>
+          <t>-26,85; -10,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-18,33; -2,49</t>
+          <t>-20,52; -4,97</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-5,82; 18,84</t>
+          <t>-19,47; 12,17</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-23,98; -12,67</t>
+          <t>-23,93; -12,15</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-17,29; -5,94</t>
+          <t>-17,35; -6,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 11,79</t>
+          <t>-5,35; 12,86</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-23,16%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-13,92%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>11,28%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-24,2%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-16,5%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>-2,67%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-23,16%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-13,92%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>-2,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,45%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-33,26; -15,37</t>
+          <t>-32,09; -12,1</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -6,37</t>
+          <t>-22,84; -2,42</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-23,56; 15,28</t>
+          <t>-8,13; 24,83</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-32,33; -13,46</t>
+          <t>-33,15; -13,99</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-23,28; -3,93</t>
+          <t>-25,05; -6,62</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-6,92; 26,23</t>
+          <t>-24,24; 15,95</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-30,34; -16,84</t>
+          <t>-30,2; -16,12</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-21,98; -7,9</t>
+          <t>-22,06; -8,32</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-8,91; 15,61</t>
+          <t>-6,63; 17,42</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-16,33</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>7,99</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-15,36</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-3,8</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-16,33</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,74</t>
+          <t>0,2</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>5,08</t>
+          <t>4,47</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-19,68; -11,26</t>
+          <t>-20,58; -12,23</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 0,15</t>
+          <t>-5,01; 3,09</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 8,7</t>
+          <t>0,87; 14,66</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-20,83; -12,2</t>
+          <t>-19,6; -11,53</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 2,84</t>
+          <t>-8,2; 0,21</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0,78; 14,08</t>
+          <t>-6,94; 7,14</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-18,86; -12,95</t>
+          <t>-18,82; -12,67</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,65</t>
+          <t>-5,35; 0,31</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 9,47</t>
+          <t>-0,49; 9,43</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-24,97%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-1,61%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>12,22%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-22,63%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-5,6%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-24,97%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-1,61%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,44; -16,81</t>
+          <t>-30,86; -19,29</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 0,22</t>
+          <t>-7,59; 4,9</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 12,95</t>
+          <t>1,61; 22,9</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-31,1; -19,09</t>
+          <t>-28,01; -17,36</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 4,52</t>
+          <t>-11,64; 0,32</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,18; 22,01</t>
+          <t>-10,14; 10,71</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-27,63; -19,71</t>
+          <t>-27,66; -19,41</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 0,99</t>
+          <t>-7,92; 0,5</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,3</t>
+          <t>-0,72; 14,41</t>
         </is>
       </c>
     </row>
